--- a/docs/Audit/v6_0/smoke_test/Profit_and_Loss Smoke Test.xlsx
+++ b/docs/Audit/v6_0/smoke_test/Profit_and_Loss Smoke Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QSTools\qstools-web\docs\Audit\v6_0\smoke_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B209BC1-C43D-4B61-B8AD-8E1764983774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FACAE65-4F5C-43E0-9D35-59FC7E40C275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="10470" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profit and Loss" sheetId="1" r:id="rId1"/>
@@ -710,7 +710,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="14">
-        <v>83183</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -747,7 +747,7 @@
       </c>
       <c r="B32" s="12">
         <f>SUM(B23:B31)</f>
-        <v>90511</v>
+        <v>111328</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13.35" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="B34" s="16">
         <f>((B16 + B20) - B32)</f>
-        <v>50901</v>
+        <v>30084</v>
       </c>
     </row>
   </sheetData>
